--- a/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon det skjedde ved), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.</t>
+    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon det skjedde ved), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.
+Dersom opplysninger om en tidligere rapportert administrering korrigeres/endres eller administreringen annulleres/slettes, skal administreringen rapporteres på nytt med samme identifikator (identifier). Ved annullering/sletting brukes status entered-in-error.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -475,13 +476,13 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
-  </si>
-  <si>
-    <t>Identifiers associated with this Medication Administration that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier.</t>
+    <t>Identifikator som entydig identifiserer legemiddeladministreringen over tid.</t>
+  </si>
+  <si>
+    <t>Identifikator som entydig identifiserer legemiddeladministreringen over tid. Identifikatoren skal beholdes dersom en tidligere rapportert administrering korrigeres/endres eller annulleres/slettes og rapporteres på nytt.</t>
+  </si>
+  <si>
+    <t>Avsender skal benytte samme identifikator ved ny rapportering av en tidligere innsendt administrering. En korrigering/endring skal ikke rapporteres som en ny administrering med ny identifikator. identifier.system bør identifisere avsenders identifikatorområde slik at identifikatoren er entydig på tvers av avsendere.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -530,13 +531,13 @@
     <t>MedicationAdministration.status</t>
   </si>
   <si>
-    <t>Status administrering (completed | entered-in-error)</t>
-  </si>
-  <si>
-    <t>Status administrering. Skal vanligvis settes til 'Gjennomført' (completed), men 'Feilregistrert' (entered-in-error) MÅ benyttes hvis registreringen inneholder en alvorlig feil og skal slettes.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>Status for legemiddeladministreringen (completed | entered-in-error)</t>
+  </si>
+  <si>
+    <t>Angir om legemiddeladministreringen er utført eller om en tidligere registrert administrering er feilregistrert. completed brukes for en utført administrering. entered-in-error brukes når en tidligere rapportert administrering skal annulleres/slettes fordi registreringen ikke representerer en gyldig administrering.</t>
+  </si>
+  <si>
+    <t>Ved korrigering/endring av opplysninger om en tidligere rapportert administrering skal ressursen rapporteres på nytt med samme identifikator (identifier) og korrigerte opplysninger. Ved annullering/sletting skal den rapporteres på nytt med samme identifikator (identifier) og status entered-in-error. En tidligere rapportert administrering skal ikke annulleres/slettes ved bare å utelate den fra senere innsendinger.</t>
   </si>
   <si>
     <t>required</t>

--- a/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon det skjedde ved), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.
+    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon episoden skjedde ved), organisasjonen administreringen ble utført ved (administrertVed, når episoden gjelder hele innleggelsen), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.
 Dersom opplysninger om en tidligere rapportert administrering korrigeres/endres eller administreringen annulleres/slettes, skal administreringen rapporteres på nytt med samme identifikator (identifier). Ved annullering/sletting brukes status entered-in-error.</t>
   </si>
   <si>
@@ -429,33 +429,57 @@
     <t>MedicationAdministration.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.extension:administrertVed</t>
+  </si>
+  <si>
+    <t>administrertVed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-administrert-ved}
+</t>
+  </si>
+  <si>
+    <t>Stedet (organisasjonen) administreringen ble utført</t>
+  </si>
+  <si>
+    <t>Administreringen refererer også til en episode, som igjen kan referere til en organisasjon. Administrert ved benyttes hvis episoden reflekterer hele innleggelsen, dvs. i tilfeller der episoden ikke gjenspeiler pasientens forflytninger (f.eks. mellom ulike avdelinger) under innleggelsen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -463,6 +487,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -785,17 +812,13 @@
     <t>MedicationAdministration.effective[x].extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1829,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.84765625" customWidth="true" bestFit="true"/>
@@ -2823,7 +2846,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2842,17 +2865,15 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2889,16 +2910,14 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2919,7 +2938,7 @@
         <v>78</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>78</v>
@@ -2931,48 +2950,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -3020,7 +3037,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3029,7 +3046,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -3038,7 +3055,7 @@
         <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>78</v>
@@ -3052,14 +3069,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3072,24 +3089,26 @@
         <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -3137,7 +3156,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3149,16 +3168,16 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>78</v>
@@ -3192,18 +3211,20 @@
         <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
@@ -3267,13 +3288,13 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -3284,10 +3305,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3298,7 +3319,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
@@ -3310,13 +3331,13 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3367,7 +3388,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3382,10 +3403,10 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3399,10 +3420,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3410,32 +3431,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3460,11 +3479,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3482,13 +3503,13 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
@@ -3503,10 +3524,10 @@
         <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -3514,10 +3535,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3525,30 +3546,32 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3573,13 +3596,11 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3597,13 +3618,13 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
@@ -3612,16 +3633,16 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -3629,10 +3650,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3643,7 +3664,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3655,13 +3676,13 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3688,11 +3709,13 @@
         <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>78</v>
@@ -3710,13 +3733,13 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>78</v>
@@ -3725,16 +3748,16 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -3742,10 +3765,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3753,7 +3776,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3765,20 +3788,18 @@
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3803,13 +3824,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3827,10 +3846,10 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>88</v>
@@ -3842,16 +3861,16 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -3859,10 +3878,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3885,15 +3904,17 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3942,7 +3963,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>88</v>
@@ -3972,7 +3993,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>206</v>
       </c>
@@ -3985,19 +4006,19 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>207</v>
@@ -4060,7 +4081,7 @@
         <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -4087,7 +4108,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>214</v>
       </c>
@@ -4103,10 +4124,10 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
@@ -4178,7 +4199,7 @@
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
@@ -4187,16 +4208,16 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4204,10 +4225,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4215,10 +4236,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -4227,16 +4248,16 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4275,23 +4296,25 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
@@ -4300,16 +4323,16 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
@@ -4317,20 +4340,18 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4345,13 +4366,13 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4390,19 +4411,17 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>88</v>
@@ -4414,19 +4433,19 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AK22" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>78</v>
@@ -4434,13 +4453,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4462,13 +4481,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4519,7 +4538,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>88</v>
@@ -4531,19 +4550,19 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>241</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -4551,12 +4570,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4574,16 +4595,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4634,10 +4655,10 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
@@ -4646,19 +4667,19 @@
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>78</v>
@@ -4666,21 +4687,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4692,17 +4713,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4739,16 +4758,16 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>250</v>
@@ -4757,19 +4776,19 @@
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4783,21 +4802,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4806,19 +4825,19 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4856,43 +4875,43 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
@@ -4900,10 +4919,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4926,92 +4945,90 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q27" t="s" s="2">
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="R27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5019,10 +5036,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5030,10 +5047,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5045,20 +5062,24 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5102,31 +5123,31 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>241</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5134,10 +5155,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5148,7 +5169,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -5157,16 +5178,16 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5217,31 +5238,31 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5249,21 +5270,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -5275,17 +5296,15 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5340,19 +5359,19 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5366,14 +5385,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5386,26 +5405,24 @@
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5453,7 +5470,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5471,7 +5488,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5485,42 +5502,46 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5544,13 +5565,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5568,25 +5589,25 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5611,7 +5632,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5623,16 +5644,16 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5659,13 +5680,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5686,7 +5707,7 @@
         <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5698,10 +5719,10 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5715,10 +5736,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5726,10 +5747,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5738,16 +5759,16 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>299</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5774,13 +5795,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>301</v>
+        <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5798,13 +5819,13 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
@@ -5822,7 +5843,7 @@
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>78</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -5830,10 +5851,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5856,17 +5877,15 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5891,13 +5910,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -5915,7 +5934,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5930,27 +5949,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AN35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5961,10 +5980,10 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
@@ -5973,16 +5992,16 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6032,13 +6051,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -6047,27 +6066,27 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO36" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6078,10 +6097,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
@@ -6090,15 +6109,17 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6147,13 +6168,13 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
@@ -6162,16 +6183,16 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6179,10 +6200,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6205,13 +6226,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6262,7 +6283,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6277,7 +6298,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>333</v>
@@ -6286,7 +6307,7 @@
         <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6294,10 +6315,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6308,7 +6329,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6320,13 +6341,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>270</v>
+        <v>336</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6377,25 +6398,25 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>337</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6409,10 +6430,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6435,13 +6456,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>240</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>241</v>
+        <v>343</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6492,7 +6513,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6504,13 +6525,13 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>243</v>
+        <v>345</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6524,21 +6545,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -6550,17 +6571,15 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6615,19 +6634,19 @@
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6641,14 +6660,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6661,26 +6680,24 @@
         <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6728,7 +6745,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6746,7 +6763,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6760,42 +6777,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>239</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6843,25 +6864,25 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6875,10 +6896,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6889,7 +6910,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6901,17 +6922,15 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6936,13 +6955,13 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6960,7 +6979,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6984,18 +7003,18 @@
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7009,7 +7028,7 @@
         <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
@@ -7018,16 +7037,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7053,14 +7072,14 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7077,7 +7096,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7095,24 +7114,24 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO45" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7126,7 +7145,7 @@
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -7135,15 +7154,17 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>240</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7168,13 +7189,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7192,7 +7213,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7204,19 +7225,19 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>243</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7224,21 +7245,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7250,17 +7271,15 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7297,16 +7316,16 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>250</v>
@@ -7315,19 +7334,19 @@
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7341,18 +7360,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>80</v>
@@ -7364,23 +7383,21 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>365</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>366</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
+        <v>255</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7416,17 +7433,19 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>257</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7438,19 +7457,19 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>372</v>
+        <v>251</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -7458,23 +7477,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -7486,19 +7503,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7535,19 +7552,17 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7565,13 +7580,13 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7579,12 +7594,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7602,19 +7619,23 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>239</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>240</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7662,31 +7683,31 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>242</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>243</v>
+        <v>379</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -7694,21 +7715,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
@@ -7720,17 +7741,15 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7767,16 +7786,16 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>250</v>
@@ -7785,19 +7804,19 @@
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7811,21 +7830,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7834,23 +7853,21 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>254</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>255</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7859,7 +7876,7 @@
         <v>78</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>78</v>
@@ -7886,43 +7903,43 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>257</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>390</v>
+        <v>251</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -7930,10 +7947,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7941,7 +7958,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>88</v>
@@ -7956,18 +7973,20 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>239</v>
+        <v>102</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7976,7 +7995,7 @@
         <v>78</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>78</v>
@@ -8015,7 +8034,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8033,13 +8052,13 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8047,10 +8066,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8058,7 +8077,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
@@ -8073,18 +8092,18 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8108,11 +8127,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8130,7 +8151,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8148,13 +8169,13 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8162,10 +8183,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8173,7 +8194,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -8188,17 +8209,17 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8223,13 +8244,11 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8247,7 +8266,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8265,13 +8284,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8279,10 +8298,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8305,19 +8324,17 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8366,7 +8383,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8384,13 +8401,13 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -8398,14 +8415,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8426,19 +8441,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>365</v>
+        <v>426</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8487,13 +8502,13 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
@@ -8505,13 +8520,13 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8519,12 +8534,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8542,19 +8559,23 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>239</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>240</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8602,31 +8623,31 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>242</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>243</v>
+        <v>379</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -8634,21 +8655,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8660,17 +8681,15 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8707,16 +8726,16 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>250</v>
@@ -8725,19 +8744,19 @@
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -8751,21 +8770,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8774,23 +8793,21 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>255</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8799,7 +8816,7 @@
         <v>78</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>78</v>
@@ -8826,43 +8843,43 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>390</v>
+        <v>251</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -8870,10 +8887,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8881,7 +8898,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -8896,18 +8913,20 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>239</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8916,7 +8935,7 @@
         <v>78</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>78</v>
@@ -8955,7 +8974,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8973,13 +8992,13 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -8987,10 +9006,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8998,7 +9017,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -9013,18 +9032,18 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9072,7 +9091,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9090,13 +9109,13 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9104,10 +9123,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9115,7 +9134,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
@@ -9130,17 +9149,17 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9189,7 +9208,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9207,13 +9226,13 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9221,10 +9240,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9247,19 +9266,17 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9308,7 +9325,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9326,13 +9343,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9340,10 +9357,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9354,7 +9371,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9366,19 +9383,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>239</v>
+        <v>426</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9427,7 +9444,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9445,13 +9462,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9459,10 +9476,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9473,7 +9490,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9482,21 +9499,23 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9520,31 +9539,31 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9562,13 +9581,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9576,10 +9595,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9587,7 +9606,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -9602,16 +9621,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9637,13 +9656,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9661,7 +9680,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9704,7 +9723,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9766,14 +9785,16 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AC68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>464</v>
@@ -9806,16 +9827,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>471</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9827,7 +9846,7 @@
         <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -9836,16 +9855,16 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L69" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9883,19 +9902,17 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9913,26 +9930,28 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>78</v>
       </c>
@@ -9941,10 +9960,10 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>78</v>
@@ -9953,16 +9972,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10012,13 +10031,13 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
@@ -10030,20 +10049,137 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10053,7 +10189,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
